--- a/data/Program Output KPIs by FTE.xlsx
+++ b/data/Program Output KPIs by FTE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z003vm8n\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BD8FCE-BA21-4359-9DA0-2E7B1C96F3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="8_{AEA8AB5D-8325-4AB0-9AB7-14EF18CF2485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1E17A44-C794-4FB5-BB00-42A011D3D781}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
   <si>
     <t>Research Outputs</t>
   </si>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>Total Full Time Equivalent (FTE)</t>
+  </si>
+  <si>
+    <t>Notional Target</t>
   </si>
 </sst>
 </file>
@@ -275,7 +278,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -291,6 +294,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -323,7 +332,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -379,9 +388,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -399,6 +405,19 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -740,18 +759,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436DF3B9-9B26-4648-BD64-23BB8D8864D3}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" style="6" customWidth="1"/>
     <col min="2" max="2" width="27" style="5" customWidth="1"/>
     <col min="3" max="3" width="36.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.77734375" style="26"/>
-    <col min="5" max="5" width="8.77734375" style="22"/>
-    <col min="6" max="6" width="8.77734375" style="18"/>
+    <col min="4" max="4" width="6.88671875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="6.77734375" style="25" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" style="21" customWidth="1"/>
+    <col min="7" max="7" width="6.77734375" style="18" customWidth="1"/>
+    <col min="8" max="10" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A1" s="10"/>
       <c r="B1" s="11" t="s">
         <v>20</v>
@@ -759,42 +780,46 @@
       <c r="C1" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="23">
+      <c r="D1" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="22">
         <v>2025</v>
       </c>
-      <c r="E1" s="23">
+      <c r="F1" s="22">
         <v>2026</v>
       </c>
-      <c r="F1" s="23">
+      <c r="G1" s="22">
         <v>2027</v>
       </c>
-      <c r="G1" s="23">
+      <c r="H1" s="22">
         <v>2028</v>
       </c>
-      <c r="H1" s="23">
+      <c r="I1" s="22">
         <v>2029</v>
       </c>
-      <c r="I1" s="23">
+      <c r="J1" s="22">
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="14"/>
-      <c r="D2" s="9">
+      <c r="D2" s="26"/>
+      <c r="E2" s="9">
         <v>133</v>
       </c>
-      <c r="E2" s="19"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="15"/>
-    </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="F2" s="19"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="15"/>
+    </row>
+    <row r="3" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -803,181 +828,202 @@
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="24">
-        <v>1.6</v>
-      </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="12"/>
+      <c r="D3" s="27">
+        <v>2</v>
+      </c>
+      <c r="E3" s="23">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="F3" s="12"/>
+      <c r="G3" s="17"/>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
-    </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="27"/>
+      <c r="J3" s="12"/>
+    </row>
+    <row r="4" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A4" s="31"/>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="27"/>
+      <c r="E4" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="21"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="17"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
-    </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A5" s="27"/>
+      <c r="J4" s="12"/>
+    </row>
+    <row r="5" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A5" s="31"/>
       <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="27"/>
+      <c r="E5" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="17"/>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
-    </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
+      <c r="J5" s="12"/>
+    </row>
+    <row r="6" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="31" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="24">
-        <v>0.8</v>
-      </c>
-      <c r="E6" s="20"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="27">
+        <v>0.84899999999999998</v>
+      </c>
+      <c r="E6" s="23">
+        <v>0.84962406015037595</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="17"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
-    </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="27"/>
+      <c r="J6" s="12"/>
+    </row>
+    <row r="7" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A7" s="32"/>
+      <c r="B7" s="31"/>
       <c r="C7" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="27"/>
+      <c r="E7" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="21"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="17"/>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
-    </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28" t="s">
+      <c r="J7" s="12"/>
+    </row>
+    <row r="8" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A8" s="32"/>
+      <c r="B8" s="32" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="24">
-        <v>0.8</v>
-      </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="12"/>
+      <c r="D8" s="28">
+        <v>0.77439999999999998</v>
+      </c>
+      <c r="E8" s="23">
+        <v>0.84962406015037595</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="17"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-    </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="28"/>
+      <c r="J8" s="12"/>
+    </row>
+    <row r="9" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A9" s="32"/>
+      <c r="B9" s="32"/>
       <c r="C9" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="28"/>
+      <c r="E9" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="21"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="17"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
-    </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28" t="s">
+      <c r="J9" s="12"/>
+    </row>
+    <row r="10" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A10" s="32"/>
+      <c r="B10" s="32" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="28">
         <v>94.8</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="12"/>
+      <c r="E10" s="23">
+        <v>94.8</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="17"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
-    </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
+      <c r="J10" s="12"/>
+    </row>
+    <row r="11" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A11" s="32"/>
+      <c r="B11" s="32"/>
       <c r="C11" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="28"/>
+      <c r="E11" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="21"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="17"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
-    </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28" t="s">
+      <c r="J11" s="12"/>
+    </row>
+    <row r="12" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A12" s="32"/>
+      <c r="B12" s="32" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="28">
         <v>10.9</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="12"/>
+      <c r="E12" s="23">
+        <v>10.9</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="17"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-    </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
+      <c r="J12" s="12"/>
+    </row>
+    <row r="13" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A13" s="32"/>
+      <c r="B13" s="32"/>
       <c r="C13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="28"/>
+      <c r="E13" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="21"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="17"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-    </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="27" t="s">
+      <c r="J13" s="12"/>
+    </row>
+    <row r="14" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A14" s="31" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -986,85 +1032,96 @@
       <c r="C14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="24">
-        <v>0.1</v>
-      </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="12"/>
+      <c r="D14" s="27">
+        <v>0.3</v>
+      </c>
+      <c r="E14" s="23">
+        <v>0.3</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="17"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
-    </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A15" s="27"/>
+      <c r="J14" s="12"/>
+    </row>
+    <row r="15" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A15" s="31"/>
       <c r="B15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="28"/>
+      <c r="E15" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="17"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
-    </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A16" s="27"/>
+      <c r="J15" s="12"/>
+    </row>
+    <row r="16" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A16" s="31"/>
       <c r="B16" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="28"/>
+      <c r="E16" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="21"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="17"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
-    </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A17" s="27"/>
+      <c r="J16" s="12"/>
+    </row>
+    <row r="17" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A17" s="31"/>
       <c r="B17" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="24">
-        <v>0.4</v>
-      </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="12"/>
+      <c r="D17" s="27">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="E17" s="23">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="17"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
-    </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A18" s="27"/>
+      <c r="J17" s="12"/>
+    </row>
+    <row r="18" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A18" s="31"/>
       <c r="B18" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="24">
-        <v>0.2</v>
-      </c>
-      <c r="E18" s="20"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="12"/>
+      <c r="D18" s="27">
+        <v>0.21</v>
+      </c>
+      <c r="E18" s="29">
+        <v>0.1729</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="17"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
-    </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+      <c r="J18" s="12"/>
+    </row>
+    <row r="19" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A19" s="31" t="s">
         <v>5</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -1073,85 +1130,100 @@
       <c r="C19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="24">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E19" s="20"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="12"/>
+      <c r="D19" s="27">
+        <v>1.052</v>
+      </c>
+      <c r="E19" s="23">
+        <v>1.052</v>
+      </c>
+      <c r="F19" s="12"/>
+      <c r="G19" s="17"/>
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
-    </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A20" s="27"/>
+      <c r="J19" s="12"/>
+    </row>
+    <row r="20" spans="1:10" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="31"/>
       <c r="B20" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="24">
-        <v>0.3</v>
-      </c>
-      <c r="E20" s="20"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="12"/>
+      <c r="D20" s="27">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="E20" s="23">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="F20" s="12"/>
+      <c r="G20" s="17"/>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
-    </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A21" s="27"/>
+      <c r="J20" s="12"/>
+    </row>
+    <row r="21" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A21" s="31"/>
       <c r="B21" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="27">
         <v>0.1</v>
       </c>
-      <c r="E21" s="20"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
+      <c r="E21" s="29">
+        <v>6.0150375939849621E-2</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="30"/>
       <c r="I21" s="12"/>
-    </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A22" s="27"/>
+      <c r="J21" s="12"/>
+    </row>
+    <row r="22" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A22" s="31"/>
       <c r="B22" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="24">
-        <v>0.1</v>
-      </c>
-      <c r="E22" s="20"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="12"/>
+      <c r="D22" s="27">
+        <v>0.23</v>
+      </c>
+      <c r="E22" s="29">
+        <v>0.13533834586466165</v>
+      </c>
+      <c r="F22" s="12"/>
+      <c r="G22" s="17"/>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
-    </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A23" s="27"/>
+      <c r="J22" s="12"/>
+    </row>
+    <row r="23" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="31"/>
       <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="24">
-        <v>0.2</v>
-      </c>
-      <c r="E23" s="20"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="12"/>
+      <c r="D23" s="28">
+        <v>0.22550000000000001</v>
+      </c>
+      <c r="E23" s="29">
+        <v>0.22556390977443608</v>
+      </c>
+      <c r="F23" s="12"/>
+      <c r="G23" s="17"/>
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
-    </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
+      <c r="J23" s="12"/>
+    </row>
+    <row r="24" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="31" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -1160,211 +1232,178 @@
       <c r="C24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="D24" s="27"/>
+      <c r="E24" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="21"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="12"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="17"/>
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
-    </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A25" s="27"/>
+      <c r="J24" s="12"/>
+    </row>
+    <row r="25" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A25" s="31"/>
       <c r="B25" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="27"/>
+      <c r="E25" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="21"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="12"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="17"/>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
-    </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A26" s="27"/>
+      <c r="J25" s="12"/>
+    </row>
+    <row r="26" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A26" s="31"/>
       <c r="B26" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="D26" s="27"/>
+      <c r="E26" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="21"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="12"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="17"/>
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A13"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A19:A23"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
   </mergeCells>
-  <conditionalFormatting sqref="D3">
-    <cfRule type="colorScale" priority="14">
+  <conditionalFormatting sqref="E3">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1"/>
-        <cfvo type="num" val="2"/>
+        <cfvo type="formula" val="$D$3/2"/>
+        <cfvo type="formula" val="$D$3"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6">
-    <cfRule type="colorScale" priority="13">
+  <conditionalFormatting sqref="E6">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.8"/>
+        <cfvo type="formula" val="$D$6/2"/>
+        <cfvo type="formula" val="$D$6"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="E8">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.8"/>
+        <cfvo type="formula" val="$D$8/2"/>
+        <cfvo type="formula" val="$D$8"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D10">
-    <cfRule type="colorScale" priority="11">
+  <conditionalFormatting sqref="E10">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="50"/>
-        <cfvo type="num" val="94.8"/>
+        <cfvo type="formula" val="$D$10/2"/>
+        <cfvo type="formula" val="$D$10"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D12">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="E12">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="5"/>
-        <cfvo type="num" val="10.9"/>
+        <cfvo type="formula" val="$D$12/2"/>
+        <cfvo type="formula" val="$D$12"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D14">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="E14">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.05"/>
-        <cfvo type="num" val="0.1"/>
+        <cfvo type="formula" val="$D$14/2"/>
+        <cfvo type="formula" val="$D$14"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D17">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="E17:E20">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.05"/>
-        <cfvo type="num" val="0.4"/>
+        <cfvo type="formula" val="$D$18/2"/>
+        <cfvo type="formula" val="$D$18"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="E21">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.28000000000000003"/>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$21/2"/>
+        <cfvo type="formula" val="$D$21"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D19">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="E22">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="1.1000000000000001"/>
+        <cfvo type="formula" val="$D$22/2"/>
+        <cfvo type="formula" val="$D$22"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D20">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="E23">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.2"/>
-        <cfvo type="num" val="0.28000000000000003"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D21">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="num" val="5.0000000000000001E-3"/>
-        <cfvo type="num" val="0.12"/>
-        <cfvo type="num" val="0.17"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D22">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.13"/>
-        <cfvo type="num" val="0.17"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D23">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.09"/>
-        <cfvo type="max"/>
+        <cfvo type="formula" val="$D$23/2"/>
+        <cfvo type="formula" val="$D$23"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>

--- a/data/Program Output KPIs by FTE.xlsx
+++ b/data/Program Output KPIs by FTE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z003vm8n\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="8_{AEA8AB5D-8325-4AB0-9AB7-14EF18CF2485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1E17A44-C794-4FB5-BB00-42A011D3D781}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E024745-60E1-4671-B3E6-0CB1DE3E531E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -107,9 +107,6 @@
     <t>Number of delivery partners trained</t>
   </si>
   <si>
-    <t>Number of delivery partners trained who are female</t>
-  </si>
-  <si>
     <t>Number of varieties released</t>
   </si>
   <si>
@@ -188,9 +185,6 @@
     <t>Number of national scientists who attended training courses</t>
   </si>
   <si>
-    <t>Number of national scientists who attended training courses who are female</t>
-  </si>
-  <si>
     <t>KPI Metric</t>
   </si>
   <si>
@@ -201,6 +195,12 @@
   </si>
   <si>
     <t>Notional Target</t>
+  </si>
+  <si>
+    <t>Percentage of delivery partners trained who are female</t>
+  </si>
+  <si>
+    <t>Percentage of national scientists who attended training courses who are female</t>
   </si>
 </sst>
 </file>
@@ -778,10 +778,10 @@
         <v>20</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E1" s="22">
         <v>2025</v>
@@ -804,7 +804,7 @@
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="14"/>
@@ -850,7 +850,7 @@
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="17"/>
@@ -868,7 +868,7 @@
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="17"/>
@@ -884,7 +884,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="27">
         <v>0.84899999999999998</v>
@@ -902,11 +902,11 @@
       <c r="A7" s="32"/>
       <c r="B7" s="31"/>
       <c r="C7" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="27"/>
       <c r="E7" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="17"/>
@@ -920,7 +920,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="28">
         <v>0.77439999999999998</v>
@@ -938,11 +938,11 @@
       <c r="A9" s="32"/>
       <c r="B9" s="32"/>
       <c r="C9" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" s="28"/>
       <c r="E9" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="17"/>
@@ -974,11 +974,11 @@
       <c r="A11" s="32"/>
       <c r="B11" s="32"/>
       <c r="C11" s="8" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="D11" s="28"/>
       <c r="E11" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="17"/>
@@ -992,7 +992,7 @@
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" s="28">
         <v>10.9</v>
@@ -1010,11 +1010,11 @@
       <c r="A13" s="32"/>
       <c r="B13" s="32"/>
       <c r="C13" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="17"/>
@@ -1027,10 +1027,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" s="27">
         <v>0.3</v>
@@ -1047,14 +1047,14 @@
     <row r="15" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A15" s="31"/>
       <c r="B15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="28"/>
       <c r="E15" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="17"/>
@@ -1065,14 +1065,14 @@
     <row r="16" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A16" s="31"/>
       <c r="B16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="28"/>
       <c r="E16" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="17"/>
@@ -1083,7 +1083,7 @@
     <row r="17" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A17" s="31"/>
       <c r="B17" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>4</v>
@@ -1103,10 +1103,10 @@
     <row r="18" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="31"/>
       <c r="B18" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" s="27">
         <v>0.21</v>
@@ -1125,10 +1125,10 @@
         <v>5</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" s="27">
         <v>1.052</v>
@@ -1145,7 +1145,7 @@
     <row r="20" spans="1:10" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="31"/>
       <c r="B20" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>6</v>
@@ -1165,10 +1165,10 @@
     <row r="21" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A21" s="31"/>
       <c r="B21" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21" s="27">
         <v>0.1</v>
@@ -1185,10 +1185,10 @@
     <row r="22" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A22" s="31"/>
       <c r="B22" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" s="27">
         <v>0.23</v>
@@ -1205,10 +1205,10 @@
     <row r="23" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A23" s="31"/>
       <c r="B23" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" s="28">
         <v>0.22550000000000001</v>
@@ -1227,14 +1227,14 @@
         <v>7</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F24" s="20"/>
       <c r="G24" s="17"/>
@@ -1245,14 +1245,14 @@
     <row r="25" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A25" s="31"/>
       <c r="B25" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F25" s="20"/>
       <c r="G25" s="17"/>
@@ -1263,14 +1263,14 @@
     <row r="26" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A26" s="31"/>
       <c r="B26" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="27"/>
       <c r="E26" s="24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F26" s="20"/>
       <c r="G26" s="17"/>
@@ -1280,15 +1280,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A13"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A19:A23"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <conditionalFormatting sqref="E3">
     <cfRule type="colorScale" priority="19">

--- a/data/Program Output KPIs by FTE.xlsx
+++ b/data/Program Output KPIs by FTE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E024745-60E1-4671-B3E6-0CB1DE3E531E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDCEDEB5-005A-4EBE-AFCF-F575B9F1FEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -110,9 +110,6 @@
     <t>Number of varieties released</t>
   </si>
   <si>
-    <t>Percentage of annual rate of genetic gain, by crop</t>
-  </si>
-  <si>
     <t>Crop Trust performance compliance rate (%)</t>
   </si>
   <si>
@@ -201,6 +198,9 @@
   </si>
   <si>
     <t>Percentage of national scientists who attended training courses who are female</t>
+  </si>
+  <si>
+    <t>Average (across crops) percentage yield-related genetic gain</t>
   </si>
 </sst>
 </file>
@@ -778,10 +778,10 @@
         <v>20</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E1" s="22">
         <v>2025</v>
@@ -804,7 +804,7 @@
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="14"/>
@@ -850,7 +850,7 @@
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="17"/>
@@ -868,7 +868,7 @@
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="17"/>
@@ -884,7 +884,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" s="27">
         <v>0.84899999999999998</v>
@@ -902,11 +902,11 @@
       <c r="A7" s="32"/>
       <c r="B7" s="31"/>
       <c r="C7" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="27"/>
       <c r="E7" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="17"/>
@@ -920,7 +920,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" s="28">
         <v>0.77439999999999998</v>
@@ -938,11 +938,11 @@
       <c r="A9" s="32"/>
       <c r="B9" s="32"/>
       <c r="C9" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" s="28"/>
       <c r="E9" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="17"/>
@@ -974,11 +974,11 @@
       <c r="A11" s="32"/>
       <c r="B11" s="32"/>
       <c r="C11" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="28"/>
       <c r="E11" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="17"/>
@@ -992,7 +992,7 @@
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" s="28">
         <v>10.9</v>
@@ -1010,11 +1010,11 @@
       <c r="A13" s="32"/>
       <c r="B13" s="32"/>
       <c r="C13" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="17"/>
@@ -1027,7 +1027,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>22</v>
@@ -1044,17 +1044,17 @@
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="31"/>
       <c r="B15" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D15" s="28"/>
       <c r="E15" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="17"/>
@@ -1065,14 +1065,14 @@
     <row r="16" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A16" s="31"/>
       <c r="B16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" s="28"/>
       <c r="E16" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="17"/>
@@ -1083,7 +1083,7 @@
     <row r="17" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A17" s="31"/>
       <c r="B17" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>4</v>
@@ -1103,10 +1103,10 @@
     <row r="18" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="31"/>
       <c r="B18" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" s="27">
         <v>0.21</v>
@@ -1125,10 +1125,10 @@
         <v>5</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D19" s="27">
         <v>1.052</v>
@@ -1145,7 +1145,7 @@
     <row r="20" spans="1:10" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="31"/>
       <c r="B20" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>6</v>
@@ -1165,10 +1165,10 @@
     <row r="21" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A21" s="31"/>
       <c r="B21" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21" s="27">
         <v>0.1</v>
@@ -1185,10 +1185,10 @@
     <row r="22" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A22" s="31"/>
       <c r="B22" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" s="27">
         <v>0.23</v>
@@ -1205,10 +1205,10 @@
     <row r="23" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A23" s="31"/>
       <c r="B23" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23" s="28">
         <v>0.22550000000000001</v>
@@ -1227,14 +1227,14 @@
         <v>7</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F24" s="20"/>
       <c r="G24" s="17"/>
@@ -1245,14 +1245,14 @@
     <row r="25" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A25" s="31"/>
       <c r="B25" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F25" s="20"/>
       <c r="G25" s="17"/>
@@ -1263,14 +1263,14 @@
     <row r="26" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A26" s="31"/>
       <c r="B26" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="27"/>
       <c r="E26" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F26" s="20"/>
       <c r="G26" s="17"/>
@@ -1280,15 +1280,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A19:A23"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="A19:A23"/>
   </mergeCells>
   <conditionalFormatting sqref="E3">
     <cfRule type="colorScale" priority="19">

--- a/data/Program Output KPIs by FTE.xlsx
+++ b/data/Program Output KPIs by FTE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDCEDEB5-005A-4EBE-AFCF-F575B9F1FEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0141DDB-8207-41A3-A5F3-F81047E172C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Research Outputs</t>
   </si>
@@ -197,7 +197,7 @@
     <t>Percentage of delivery partners trained who are female</t>
   </si>
   <si>
-    <t>Percentage of national scientists who attended training courses who are female</t>
+    <t>Pecentage of national scientists who attended training courses who are female</t>
   </si>
   <si>
     <t>Average (across crops) percentage yield-related genetic gain</t>
@@ -209,9 +209,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -304,7 +304,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -327,12 +327,178 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -356,45 +522,31 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -405,29 +557,163 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -764,534 +1050,560 @@
   <cols>
     <col min="1" max="1" width="22" style="6" customWidth="1"/>
     <col min="2" max="2" width="27" style="5" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.21875" style="5" customWidth="1"/>
     <col min="4" max="4" width="6.88671875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="6.77734375" style="25" customWidth="1"/>
-    <col min="6" max="6" width="6.77734375" style="21" customWidth="1"/>
-    <col min="7" max="7" width="6.77734375" style="18" customWidth="1"/>
+    <col min="5" max="5" width="6.77734375" style="21" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" style="13" customWidth="1"/>
+    <col min="7" max="7" width="6.77734375" style="11" customWidth="1"/>
     <col min="8" max="10" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="10"/>
-      <c r="B1" s="11" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="27"/>
+      <c r="B1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="22">
+      <c r="E1" s="65">
         <v>2025</v>
       </c>
-      <c r="F1" s="22">
+      <c r="F1" s="65">
         <v>2026</v>
       </c>
-      <c r="G1" s="22">
+      <c r="G1" s="30">
         <v>2027</v>
       </c>
-      <c r="H1" s="22">
+      <c r="H1" s="30">
         <v>2028</v>
       </c>
-      <c r="I1" s="22">
+      <c r="I1" s="30">
         <v>2029</v>
       </c>
-      <c r="J1" s="22">
+      <c r="J1" s="31">
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="9">
+      <c r="B2" s="33"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="34">
         <v>133</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="15"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="39"/>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="41">
         <v>2</v>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="42">
+        <f>217/133</f>
         <v>1.631578947368421</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="45"/>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
+      <c r="A4" s="67"/>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="24" t="s">
+      <c r="D4" s="14"/>
+      <c r="E4" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-    </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A5" s="31"/>
-      <c r="B5" s="3" t="s">
+      <c r="F4" s="9"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="46"/>
+    </row>
+    <row r="5" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="68"/>
+      <c r="B5" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="27"/>
-      <c r="E5" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
+      <c r="D5" s="48">
+        <v>0.09</v>
+      </c>
+      <c r="E5" s="49">
+        <f>6/133</f>
+        <v>4.5112781954887216E-2</v>
+      </c>
+      <c r="F5" s="50"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="27">
-        <v>0.84899999999999998</v>
-      </c>
-      <c r="E6" s="23">
+      <c r="D6" s="41">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E6" s="42">
+        <f>113/133</f>
         <v>0.84962406015037595</v>
       </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="45"/>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
-      <c r="B7" s="31"/>
+      <c r="A7" s="70"/>
+      <c r="B7" s="73"/>
       <c r="C7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
+      <c r="D7" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="22">
+        <v>0.59</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="46"/>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A8" s="32"/>
-      <c r="B8" s="32" t="s">
+      <c r="A8" s="70"/>
+      <c r="B8" s="74" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="15">
         <v>0.77439999999999998</v>
       </c>
-      <c r="E8" s="23">
-        <v>0.84962406015037595</v>
-      </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
+      <c r="E8" s="19">
+        <f>103/133</f>
+        <v>0.77443609022556392</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
-      <c r="B9" s="32"/>
+      <c r="A9" s="70"/>
+      <c r="B9" s="74"/>
       <c r="C9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="28"/>
-      <c r="E9" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
+      <c r="D9" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="E9" s="17">
+        <v>0.49</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="46"/>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="32"/>
-      <c r="B10" s="32" t="s">
+      <c r="A10" s="70"/>
+      <c r="B10" s="74" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="15">
         <v>94.8</v>
       </c>
-      <c r="E10" s="23">
-        <v>94.8</v>
-      </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-    </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A11" s="32"/>
-      <c r="B11" s="32"/>
+      <c r="E10" s="19">
+        <f>12612/133</f>
+        <v>94.827067669172934</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="46"/>
+    </row>
+    <row r="11" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A11" s="70"/>
+      <c r="B11" s="74"/>
       <c r="C11" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
+      <c r="D11" s="24">
+        <v>0.46</v>
+      </c>
+      <c r="E11" s="17">
+        <v>0.44</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="46"/>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A12" s="32"/>
-      <c r="B12" s="32" t="s">
+      <c r="A12" s="70"/>
+      <c r="B12" s="74" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="15">
         <v>10.9</v>
       </c>
-      <c r="E12" s="23">
-        <v>10.9</v>
-      </c>
-      <c r="F12" s="12"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-    </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="8" t="s">
+      <c r="E12" s="19">
+        <f>1444/133</f>
+        <v>10.857142857142858</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="46"/>
+    </row>
+    <row r="13" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="71"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
+      <c r="D13" s="55">
+        <v>0.51</v>
+      </c>
+      <c r="E13" s="56">
+        <v>0.34</v>
+      </c>
+      <c r="F13" s="50"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="52"/>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="41">
         <v>0.3</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="42">
         <v>0.3</v>
       </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-    </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="31"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="45"/>
+    </row>
+    <row r="15" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A15" s="67"/>
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="28"/>
-      <c r="E15" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
+      <c r="D15" s="26">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E15" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F15" s="9"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="46"/>
     </row>
     <row r="16" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A16" s="31"/>
+      <c r="A16" s="67"/>
       <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
+      <c r="D16" s="25">
+        <v>1</v>
+      </c>
+      <c r="E16" s="17">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="46"/>
     </row>
     <row r="17" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
+      <c r="A17" s="67"/>
       <c r="B17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="14">
         <v>0.38300000000000001</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="19">
         <v>0.38300000000000001</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-    </row>
-    <row r="18" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A18" s="31"/>
-      <c r="B18" s="3" t="s">
+      <c r="F17" s="9"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="46"/>
+    </row>
+    <row r="18" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="68"/>
+      <c r="B18" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="48">
         <v>0.21</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="58">
         <v>0.1729</v>
       </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="52"/>
     </row>
     <row r="19" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="41">
         <v>1.052</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="42">
         <v>1.052</v>
       </c>
-      <c r="F19" s="12"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="45"/>
     </row>
     <row r="20" spans="1:10" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="31"/>
+      <c r="A20" s="67"/>
       <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="14">
         <v>0.28499999999999998</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="19">
         <v>0.28499999999999998</v>
       </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="46"/>
     </row>
     <row r="21" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A21" s="31"/>
+      <c r="A21" s="67"/>
       <c r="B21" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="27">
-        <v>0.1</v>
-      </c>
-      <c r="E21" s="29">
+      <c r="D21" s="14">
+        <v>0.08</v>
+      </c>
+      <c r="E21" s="19">
         <v>6.0150375939849621E-2</v>
       </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-    </row>
-    <row r="22" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A22" s="31"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="46"/>
+    </row>
+    <row r="22" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A22" s="67"/>
       <c r="B22" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="14">
         <v>0.23</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="19">
         <v>0.13533834586466165</v>
       </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-    </row>
-    <row r="23" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A23" s="31"/>
-      <c r="B23" s="3" t="s">
+      <c r="F22" s="9"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="46"/>
+    </row>
+    <row r="23" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="68"/>
+      <c r="B23" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="59">
         <v>0.22550000000000001</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="58">
         <v>0.22556390977443608</v>
       </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="52"/>
     </row>
     <row r="24" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F24" s="20"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
+      <c r="D24" s="60">
+        <v>0.42</v>
+      </c>
+      <c r="E24" s="61">
+        <v>0.42</v>
+      </c>
+      <c r="F24" s="62"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="45"/>
     </row>
     <row r="25" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A25" s="31"/>
+      <c r="A25" s="67"/>
       <c r="B25" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="27"/>
-      <c r="E25" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="20"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-    </row>
-    <row r="26" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A26" s="31"/>
-      <c r="B26" s="3" t="s">
+      <c r="D25" s="24">
+        <v>0.36</v>
+      </c>
+      <c r="E25" s="17">
+        <v>0.36</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="46"/>
+    </row>
+    <row r="26" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="68"/>
+      <c r="B26" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F26" s="20"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
+      <c r="D26" s="63">
+        <v>0.13</v>
+      </c>
+      <c r="E26" s="56">
+        <v>0.11</v>
+      </c>
+      <c r="F26" s="64"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="A19:A23"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A19:A23"/>
   </mergeCells>
   <conditionalFormatting sqref="E3">
-    <cfRule type="colorScale" priority="19">
+    <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$3/2"/>
@@ -1302,8 +1614,32 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E4">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$4/2"/>
+        <cfvo type="formula" val="$D$4"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$5/2"/>
+        <cfvo type="formula" val="$D$5"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$6/2"/>
@@ -1314,8 +1650,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$7/2"/>
+        <cfvo type="formula" val="$D$7"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$8/2"/>
@@ -1326,8 +1674,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$9/2"/>
+        <cfvo type="formula" val="$D$9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$10/2"/>
@@ -1338,8 +1698,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E11">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$11"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E12">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$12/2"/>
@@ -1350,8 +1720,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="$D$13/2"/>
+        <cfvo type="formula" val="$D$13"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$14/2"/>
@@ -1362,8 +1742,32 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E15">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$15/2"/>
+        <cfvo type="formula" val="$D$15"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$16/2"/>
+        <cfvo type="formula" val="$D$16"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E17:E20">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$18/2"/>
@@ -1375,19 +1779,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
         <cfvo type="formula" val="$D$21/2"/>
         <cfvo type="formula" val="$D$21"/>
+        <color rgb="FFFFFF00"/>
         <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22">
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$22/2"/>
@@ -1399,11 +1801,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E23">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$23/2"/>
         <cfvo type="formula" val="$D$23"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E24">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$24/2"/>
+        <cfvo type="formula" val="$D$24"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E25">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$25/2"/>
+        <cfvo type="formula" val="$D$25"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E26">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$26/2"/>
+        <cfvo type="formula" val="$D$26"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>

--- a/data/Program Output KPIs by FTE.xlsx
+++ b/data/Program Output KPIs by FTE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0141DDB-8207-41A3-A5F3-F81047E172C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33CA087-CB5E-4C3C-88D2-F0A350241A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -679,6 +679,18 @@
     <xf numFmtId="1" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -695,18 +707,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1105,7 +1105,7 @@
       <c r="J2" s="39"/>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="70" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="40" t="s">
@@ -1128,7 +1128,7 @@
       <c r="J3" s="45"/>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="67"/>
+      <c r="A4" s="71"/>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
@@ -1146,7 +1146,7 @@
       <c r="J4" s="46"/>
     </row>
     <row r="5" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="68"/>
+      <c r="A5" s="72"/>
       <c r="B5" s="47" t="s">
         <v>13</v>
       </c>
@@ -1167,10 +1167,10 @@
       <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A6" s="69" t="s">
+      <c r="A6" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="66" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="40" t="s">
@@ -1190,8 +1190,8 @@
       <c r="J6" s="45"/>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A7" s="70"/>
-      <c r="B7" s="73"/>
+      <c r="A7" s="74"/>
+      <c r="B7" s="67"/>
       <c r="C7" s="7" t="s">
         <v>44</v>
       </c>
@@ -1208,8 +1208,8 @@
       <c r="J7" s="46"/>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A8" s="70"/>
-      <c r="B8" s="74" t="s">
+      <c r="A8" s="74"/>
+      <c r="B8" s="68" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1229,8 +1229,8 @@
       <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A9" s="70"/>
-      <c r="B9" s="74"/>
+      <c r="A9" s="74"/>
+      <c r="B9" s="68"/>
       <c r="C9" s="8" t="s">
         <v>42</v>
       </c>
@@ -1247,8 +1247,8 @@
       <c r="J9" s="46"/>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="70"/>
-      <c r="B10" s="74" t="s">
+      <c r="A10" s="74"/>
+      <c r="B10" s="68" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -1268,8 +1268,8 @@
       <c r="J10" s="46"/>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A11" s="70"/>
-      <c r="B11" s="74"/>
+      <c r="A11" s="74"/>
+      <c r="B11" s="68"/>
       <c r="C11" s="8" t="s">
         <v>51</v>
       </c>
@@ -1286,8 +1286,8 @@
       <c r="J11" s="46"/>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A12" s="70"/>
-      <c r="B12" s="74" t="s">
+      <c r="A12" s="74"/>
+      <c r="B12" s="68" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -1307,8 +1307,8 @@
       <c r="J12" s="46"/>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="71"/>
-      <c r="B13" s="75"/>
+      <c r="A13" s="75"/>
+      <c r="B13" s="69"/>
       <c r="C13" s="54" t="s">
         <v>52</v>
       </c>
@@ -1325,7 +1325,7 @@
       <c r="J13" s="52"/>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="70" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="40" t="s">
@@ -1347,7 +1347,7 @@
       <c r="J14" s="45"/>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A15" s="67"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="E15" s="18">
-        <v>1.4999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="10"/>
@@ -1367,7 +1367,7 @@
       <c r="J15" s="46"/>
     </row>
     <row r="16" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A16" s="67"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
@@ -1387,7 +1387,7 @@
       <c r="J16" s="46"/>
     </row>
     <row r="17" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A17" s="67"/>
+      <c r="A17" s="71"/>
       <c r="B17" s="3" t="s">
         <v>32</v>
       </c>
@@ -1407,7 +1407,7 @@
       <c r="J17" s="46"/>
     </row>
     <row r="18" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="68"/>
+      <c r="A18" s="72"/>
       <c r="B18" s="47" t="s">
         <v>33</v>
       </c>
@@ -1427,7 +1427,7 @@
       <c r="J18" s="52"/>
     </row>
     <row r="19" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A19" s="66" t="s">
+      <c r="A19" s="70" t="s">
         <v>5</v>
       </c>
       <c r="B19" s="40" t="s">
@@ -1449,7 +1449,7 @@
       <c r="J19" s="45"/>
     </row>
     <row r="20" spans="1:10" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="67"/>
+      <c r="A20" s="71"/>
       <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
@@ -1469,7 +1469,7 @@
       <c r="J20" s="46"/>
     </row>
     <row r="21" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A21" s="67"/>
+      <c r="A21" s="71"/>
       <c r="B21" s="3" t="s">
         <v>36</v>
       </c>
@@ -1489,7 +1489,7 @@
       <c r="J21" s="46"/>
     </row>
     <row r="22" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A22" s="67"/>
+      <c r="A22" s="71"/>
       <c r="B22" s="3" t="s">
         <v>37</v>
       </c>
@@ -1509,7 +1509,7 @@
       <c r="J22" s="46"/>
     </row>
     <row r="23" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="68"/>
+      <c r="A23" s="72"/>
       <c r="B23" s="47" t="s">
         <v>38</v>
       </c>
@@ -1529,7 +1529,7 @@
       <c r="J23" s="52"/>
     </row>
     <row r="24" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="66" t="s">
+      <c r="A24" s="70" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="40" t="s">
@@ -1551,7 +1551,7 @@
       <c r="J24" s="45"/>
     </row>
     <row r="25" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A25" s="67"/>
+      <c r="A25" s="71"/>
       <c r="B25" s="3" t="s">
         <v>40</v>
       </c>
@@ -1571,7 +1571,7 @@
       <c r="J25" s="46"/>
     </row>
     <row r="26" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="68"/>
+      <c r="A26" s="72"/>
       <c r="B26" s="47" t="s">
         <v>41</v>
       </c>
@@ -1592,15 +1592,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A19:A23"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="A19:A23"/>
   </mergeCells>
   <conditionalFormatting sqref="E3">
     <cfRule type="colorScale" priority="31">

--- a/data/Program Output KPIs by FTE.xlsx
+++ b/data/Program Output KPIs by FTE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33CA087-CB5E-4C3C-88D2-F0A350241A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6762A0A-9933-42BD-9A08-01DA242C003C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -679,6 +679,24 @@
     <xf numFmtId="1" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -689,24 +707,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1096,7 +1096,7 @@
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
       <c r="E2" s="34">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F2" s="35"/>
       <c r="G2" s="36"/>
@@ -1105,7 +1105,7 @@
       <c r="J2" s="39"/>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="66" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="40" t="s">
@@ -1128,7 +1128,7 @@
       <c r="J3" s="45"/>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="71"/>
+      <c r="A4" s="67"/>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
@@ -1146,7 +1146,7 @@
       <c r="J4" s="46"/>
     </row>
     <row r="5" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="72"/>
+      <c r="A5" s="68"/>
       <c r="B5" s="47" t="s">
         <v>13</v>
       </c>
@@ -1167,10 +1167,10 @@
       <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="72" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="40" t="s">
@@ -1190,8 +1190,8 @@
       <c r="J6" s="45"/>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A7" s="74"/>
-      <c r="B7" s="67"/>
+      <c r="A7" s="70"/>
+      <c r="B7" s="73"/>
       <c r="C7" s="7" t="s">
         <v>44</v>
       </c>
@@ -1208,8 +1208,8 @@
       <c r="J7" s="46"/>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A8" s="74"/>
-      <c r="B8" s="68" t="s">
+      <c r="A8" s="70"/>
+      <c r="B8" s="74" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1219,8 +1219,7 @@
         <v>0.77439999999999998</v>
       </c>
       <c r="E8" s="19">
-        <f>103/133</f>
-        <v>0.77443609022556392</v>
+        <v>0.7</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="10"/>
@@ -1229,8 +1228,8 @@
       <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A9" s="74"/>
-      <c r="B9" s="68"/>
+      <c r="A9" s="70"/>
+      <c r="B9" s="74"/>
       <c r="C9" s="8" t="s">
         <v>42</v>
       </c>
@@ -1247,8 +1246,8 @@
       <c r="J9" s="46"/>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="74"/>
-      <c r="B10" s="68" t="s">
+      <c r="A10" s="70"/>
+      <c r="B10" s="74" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -1258,8 +1257,7 @@
         <v>94.8</v>
       </c>
       <c r="E10" s="19">
-        <f>12612/133</f>
-        <v>94.827067669172934</v>
+        <v>89.4</v>
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="10"/>
@@ -1268,8 +1266,8 @@
       <c r="J10" s="46"/>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A11" s="74"/>
-      <c r="B11" s="68"/>
+      <c r="A11" s="70"/>
+      <c r="B11" s="74"/>
       <c r="C11" s="8" t="s">
         <v>51</v>
       </c>
@@ -1286,8 +1284,8 @@
       <c r="J11" s="46"/>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A12" s="74"/>
-      <c r="B12" s="68" t="s">
+      <c r="A12" s="70"/>
+      <c r="B12" s="74" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -1307,8 +1305,8 @@
       <c r="J12" s="46"/>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="75"/>
-      <c r="B13" s="69"/>
+      <c r="A13" s="71"/>
+      <c r="B13" s="75"/>
       <c r="C13" s="54" t="s">
         <v>52</v>
       </c>
@@ -1325,7 +1323,7 @@
       <c r="J13" s="52"/>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="70" t="s">
+      <c r="A14" s="66" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="40" t="s">
@@ -1347,7 +1345,7 @@
       <c r="J14" s="45"/>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A15" s="71"/>
+      <c r="A15" s="67"/>
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
@@ -1367,7 +1365,7 @@
       <c r="J15" s="46"/>
     </row>
     <row r="16" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A16" s="71"/>
+      <c r="A16" s="67"/>
       <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
@@ -1387,7 +1385,7 @@
       <c r="J16" s="46"/>
     </row>
     <row r="17" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A17" s="71"/>
+      <c r="A17" s="67"/>
       <c r="B17" s="3" t="s">
         <v>32</v>
       </c>
@@ -1407,7 +1405,7 @@
       <c r="J17" s="46"/>
     </row>
     <row r="18" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="72"/>
+      <c r="A18" s="68"/>
       <c r="B18" s="47" t="s">
         <v>33</v>
       </c>
@@ -1427,7 +1425,7 @@
       <c r="J18" s="52"/>
     </row>
     <row r="19" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A19" s="70" t="s">
+      <c r="A19" s="66" t="s">
         <v>5</v>
       </c>
       <c r="B19" s="40" t="s">
@@ -1449,7 +1447,7 @@
       <c r="J19" s="45"/>
     </row>
     <row r="20" spans="1:10" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="71"/>
+      <c r="A20" s="67"/>
       <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
@@ -1469,7 +1467,7 @@
       <c r="J20" s="46"/>
     </row>
     <row r="21" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A21" s="71"/>
+      <c r="A21" s="67"/>
       <c r="B21" s="3" t="s">
         <v>36</v>
       </c>
@@ -1489,7 +1487,7 @@
       <c r="J21" s="46"/>
     </row>
     <row r="22" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A22" s="71"/>
+      <c r="A22" s="67"/>
       <c r="B22" s="3" t="s">
         <v>37</v>
       </c>
@@ -1509,7 +1507,7 @@
       <c r="J22" s="46"/>
     </row>
     <row r="23" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="72"/>
+      <c r="A23" s="68"/>
       <c r="B23" s="47" t="s">
         <v>38</v>
       </c>
@@ -1529,7 +1527,7 @@
       <c r="J23" s="52"/>
     </row>
     <row r="24" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="70" t="s">
+      <c r="A24" s="66" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="40" t="s">
@@ -1551,7 +1549,7 @@
       <c r="J24" s="45"/>
     </row>
     <row r="25" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A25" s="71"/>
+      <c r="A25" s="67"/>
       <c r="B25" s="3" t="s">
         <v>40</v>
       </c>
@@ -1571,7 +1569,7 @@
       <c r="J25" s="46"/>
     </row>
     <row r="26" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="72"/>
+      <c r="A26" s="68"/>
       <c r="B26" s="47" t="s">
         <v>41</v>
       </c>
@@ -1592,6 +1590,7 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A24:A26"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A13"/>
     <mergeCell ref="A14:A18"/>
@@ -1600,7 +1599,6 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A24:A26"/>
   </mergeCells>
   <conditionalFormatting sqref="E3">
     <cfRule type="colorScale" priority="31">

--- a/data/Program Output KPIs by FTE.xlsx
+++ b/data/Program Output KPIs by FTE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6762A0A-9933-42BD-9A08-01DA242C003C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94262CFB-D5E7-4533-BF9B-2348D24D8327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -188,9 +188,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Total Full Time Equivalent (FTE)</t>
-  </si>
-  <si>
     <t>Notional Target</t>
   </si>
   <si>
@@ -201,6 +198,9 @@
   </si>
   <si>
     <t>Average (across crops) percentage yield-related genetic gain</t>
+  </si>
+  <si>
+    <t>Total Full Time Equivalent</t>
   </si>
 </sst>
 </file>
@@ -1067,7 +1067,7 @@
         <v>47</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E1" s="65">
         <v>2025</v>
@@ -1088,9 +1088,9 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="32" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="28"/>
@@ -1269,7 +1269,7 @@
       <c r="A11" s="70"/>
       <c r="B11" s="74"/>
       <c r="C11" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" s="24">
         <v>0.46</v>
@@ -1308,7 +1308,7 @@
       <c r="A13" s="71"/>
       <c r="B13" s="75"/>
       <c r="C13" s="54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" s="55">
         <v>0.51</v>
@@ -1350,7 +1350,7 @@
         <v>30</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="26">
         <v>1.4999999999999999E-2</v>
@@ -1590,15 +1590,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A13"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A19:A23"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <conditionalFormatting sqref="E3">
     <cfRule type="colorScale" priority="31">

--- a/data/Program Output KPIs by FTE.xlsx
+++ b/data/Program Output KPIs by FTE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94262CFB-D5E7-4533-BF9B-2348D24D8327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B14545-5415-4732-98C1-BBA220A7E2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Research Outputs</t>
   </si>
@@ -186,9 +186,6 @@
   </si>
   <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>Notional Target</t>
   </si>
   <si>
     <t>Percentage of delivery partners trained who are female</t>
@@ -278,7 +275,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,12 +294,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -498,7 +489,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -535,12 +526,6 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -560,27 +545,12 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -612,9 +582,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -629,9 +596,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -646,9 +610,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -658,27 +619,30 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -695,18 +659,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1045,801 +997,726 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436DF3B9-9B26-4648-BD64-23BB8D8864D3}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" style="6" customWidth="1"/>
     <col min="2" max="2" width="27" style="5" customWidth="1"/>
     <col min="3" max="3" width="41.21875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="6.77734375" style="21" customWidth="1"/>
-    <col min="6" max="6" width="6.77734375" style="13" customWidth="1"/>
-    <col min="7" max="7" width="6.77734375" style="11" customWidth="1"/>
-    <col min="8" max="10" width="6.77734375" customWidth="1"/>
+    <col min="4" max="4" width="6.77734375" style="19" customWidth="1"/>
+    <col min="5" max="5" width="6.77734375" style="13" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" style="11" customWidth="1"/>
+    <col min="7" max="9" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27"/>
-      <c r="B1" s="28" t="s">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="21"/>
+      <c r="B1" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="65">
+      <c r="D1" s="52">
         <v>2025</v>
       </c>
-      <c r="F1" s="65">
+      <c r="E1" s="52">
         <v>2026</v>
       </c>
-      <c r="G1" s="30">
+      <c r="F1" s="23">
         <v>2027</v>
       </c>
-      <c r="H1" s="30">
+      <c r="G1" s="23">
         <v>2028</v>
       </c>
-      <c r="I1" s="30">
+      <c r="H1" s="23">
         <v>2029</v>
       </c>
-      <c r="J1" s="31">
+      <c r="I1" s="24">
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="34">
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="27">
         <v>141</v>
       </c>
-      <c r="F2" s="35"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="39"/>
-    </row>
-    <row r="3" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="66" t="s">
+      <c r="E2" s="28"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="32"/>
+    </row>
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A3" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="41">
-        <v>2</v>
-      </c>
-      <c r="E3" s="42">
+      <c r="D3" s="34">
         <f>217/133</f>
         <v>1.631578947368421</v>
       </c>
-      <c r="F3" s="43"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="45"/>
-    </row>
-    <row r="4" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="67"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="37"/>
+    </row>
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A4" s="58"/>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="20" t="s">
+      <c r="D4" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="9"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="46"/>
-    </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="68"/>
-      <c r="B5" s="47" t="s">
+      <c r="I4" s="38"/>
+    </row>
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="59"/>
+      <c r="B5" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="48">
-        <v>0.09</v>
-      </c>
-      <c r="E5" s="49">
+      <c r="D5" s="40">
         <f>6/133</f>
         <v>4.5112781954887216E-2</v>
       </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="52"/>
-    </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A6" s="69" t="s">
+      <c r="E5" s="41"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="43"/>
+    </row>
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="41">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E6" s="42">
+      <c r="D6" s="34">
         <f>113/133</f>
         <v>0.84962406015037595</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="45"/>
-    </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A7" s="70"/>
-      <c r="B7" s="73"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="37"/>
+    </row>
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A7" s="61"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="22">
+      <c r="D7" s="20">
         <v>0.59</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="9"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="46"/>
-    </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A8" s="70"/>
-      <c r="B8" s="74" t="s">
+      <c r="I7" s="38"/>
+    </row>
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A8" s="61"/>
+      <c r="B8" s="55" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="15">
-        <v>0.77439999999999998</v>
-      </c>
-      <c r="E8" s="19">
+      <c r="D8" s="17">
         <v>0.7</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="10"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="9"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="46"/>
-    </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A9" s="70"/>
-      <c r="B9" s="74"/>
+      <c r="I8" s="38"/>
+    </row>
+    <row r="9" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A9" s="61"/>
+      <c r="B9" s="55"/>
       <c r="C9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="23">
-        <v>0.4</v>
-      </c>
-      <c r="E9" s="17">
+      <c r="D9" s="15">
         <v>0.49</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="9"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="46"/>
-    </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="70"/>
-      <c r="B10" s="74" t="s">
+      <c r="I9" s="38"/>
+    </row>
+    <row r="10" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A10" s="61"/>
+      <c r="B10" s="55" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="15">
-        <v>94.8</v>
-      </c>
-      <c r="E10" s="19">
+      <c r="D10" s="17">
         <v>89.4</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="9"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="46"/>
-    </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A11" s="70"/>
-      <c r="B11" s="74"/>
+      <c r="I10" s="38"/>
+    </row>
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A11" s="61"/>
+      <c r="B11" s="55"/>
       <c r="C11" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="24">
-        <v>0.46</v>
-      </c>
-      <c r="E11" s="17">
+        <v>49</v>
+      </c>
+      <c r="D11" s="15">
         <v>0.44</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="9"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="46"/>
-    </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A12" s="70"/>
-      <c r="B12" s="74" t="s">
+      <c r="I11" s="38"/>
+    </row>
+    <row r="12" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A12" s="61"/>
+      <c r="B12" s="55" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="15">
-        <v>10.9</v>
-      </c>
-      <c r="E12" s="19">
+      <c r="D12" s="17">
         <f>1444/133</f>
         <v>10.857142857142858</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="9"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="46"/>
-    </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="71"/>
-      <c r="B13" s="75"/>
-      <c r="C13" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="55">
-        <v>0.51</v>
-      </c>
-      <c r="E13" s="56">
+      <c r="I12" s="38"/>
+    </row>
+    <row r="13" spans="1:9" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="62"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="46">
         <v>0.34</v>
       </c>
-      <c r="F13" s="50"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="52"/>
-    </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="66" t="s">
+      <c r="E13" s="41"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="43"/>
+    </row>
+    <row r="14" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A14" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="34">
         <v>0.3</v>
       </c>
-      <c r="E14" s="42">
-        <v>0.3</v>
-      </c>
-      <c r="F14" s="43"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="45"/>
-    </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A15" s="67"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="37"/>
+    </row>
+    <row r="15" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A15" s="58"/>
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="26">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="E15" s="18">
+        <v>51</v>
+      </c>
+      <c r="D15" s="16">
         <v>1.2E-2</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="10"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="9"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="46"/>
-    </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A16" s="67"/>
+      <c r="I15" s="38"/>
+    </row>
+    <row r="16" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A16" s="58"/>
       <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="15">
         <v>1</v>
       </c>
-      <c r="E16" s="17">
-        <v>1</v>
-      </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="10"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="9"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="46"/>
-    </row>
-    <row r="17" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A17" s="67"/>
+      <c r="I16" s="38"/>
+    </row>
+    <row r="17" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A17" s="58"/>
       <c r="B17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="17">
         <v>0.38300000000000001</v>
       </c>
-      <c r="E17" s="19">
-        <v>0.38300000000000001</v>
-      </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="10"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="9"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="46"/>
-    </row>
-    <row r="18" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="68"/>
-      <c r="B18" s="47" t="s">
+      <c r="I17" s="38"/>
+    </row>
+    <row r="18" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="59"/>
+      <c r="B18" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="47" t="s">
+      <c r="C18" s="39" t="s">
         <v>24</v>
       </c>
       <c r="D18" s="48">
-        <v>0.21</v>
-      </c>
-      <c r="E18" s="58">
         <v>0.1729</v>
       </c>
-      <c r="F18" s="50"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="52"/>
-    </row>
-    <row r="19" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A19" s="66" t="s">
+      <c r="E18" s="41"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="43"/>
+    </row>
+    <row r="19" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A19" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="34">
         <v>1.052</v>
       </c>
-      <c r="E19" s="42">
-        <v>1.052</v>
-      </c>
-      <c r="F19" s="43"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="45"/>
-    </row>
-    <row r="20" spans="1:10" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="67"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="37"/>
+    </row>
+    <row r="20" spans="1:9" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="58"/>
       <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="17">
         <v>0.28499999999999998</v>
       </c>
-      <c r="E20" s="19">
-        <v>0.28499999999999998</v>
-      </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="10"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="9"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="46"/>
-    </row>
-    <row r="21" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A21" s="67"/>
+      <c r="I20" s="38"/>
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A21" s="58"/>
       <c r="B21" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="14">
-        <v>0.08</v>
-      </c>
-      <c r="E21" s="19">
+      <c r="D21" s="17">
         <v>6.0150375939849621E-2</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="46"/>
-    </row>
-    <row r="22" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A22" s="67"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="38"/>
+    </row>
+    <row r="22" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A22" s="58"/>
       <c r="B22" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="14">
-        <v>0.23</v>
-      </c>
-      <c r="E22" s="19">
+      <c r="D22" s="17">
         <v>0.13533834586466165</v>
       </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="10"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="9"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="46"/>
-    </row>
-    <row r="23" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="68"/>
-      <c r="B23" s="47" t="s">
+      <c r="I22" s="38"/>
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="59"/>
+      <c r="B23" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="53" t="s">
+      <c r="C23" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="59">
-        <v>0.22550000000000001</v>
-      </c>
-      <c r="E23" s="58">
+      <c r="D23" s="48">
         <v>0.22556390977443608</v>
       </c>
-      <c r="F23" s="50"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="52"/>
-    </row>
-    <row r="24" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="66" t="s">
+      <c r="E23" s="41"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="43"/>
+    </row>
+    <row r="24" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="60">
+      <c r="D24" s="49">
         <v>0.42</v>
       </c>
-      <c r="E24" s="61">
-        <v>0.42</v>
-      </c>
-      <c r="F24" s="62"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="45"/>
-    </row>
-    <row r="25" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A25" s="67"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="37"/>
+    </row>
+    <row r="25" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A25" s="58"/>
       <c r="B25" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="15">
         <v>0.36</v>
       </c>
-      <c r="E25" s="17">
-        <v>0.36</v>
-      </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="10"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="9"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="46"/>
-    </row>
-    <row r="26" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="68"/>
-      <c r="B26" s="47" t="s">
+      <c r="I25" s="38"/>
+    </row>
+    <row r="26" spans="1:9" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="59"/>
+      <c r="B26" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C26" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="63">
-        <v>0.13</v>
-      </c>
-      <c r="E26" s="56">
+      <c r="D26" s="46">
         <v>0.11</v>
       </c>
-      <c r="F26" s="64"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="52"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A19:A23"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="A19:A23"/>
   </mergeCells>
-  <conditionalFormatting sqref="E3">
+  <conditionalFormatting sqref="D3">
     <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$3/2"/>
-        <cfvo type="formula" val="$D$3"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$4/2"/>
-        <cfvo type="formula" val="$D$4"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$5/2"/>
-        <cfvo type="formula" val="$D$5"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$6/2"/>
-        <cfvo type="formula" val="$D$6"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$7/2"/>
-        <cfvo type="formula" val="$D$7"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$8/2"/>
-        <cfvo type="formula" val="$D$8"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$9/2"/>
-        <cfvo type="formula" val="$D$9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$10/2"/>
-        <cfvo type="formula" val="$D$10"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$11"/>
+        <cfvo type="formula" val="#REF!"/>
         <color rgb="FF92D050"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E12">
+  <conditionalFormatting sqref="D12">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$12/2"/>
-        <cfvo type="formula" val="$D$12"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13">
     <cfRule type="colorScale" priority="6">
       <colorScale>
-        <cfvo type="formula" val="$D$13/2"/>
-        <cfvo type="formula" val="$D$13"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$14/2"/>
-        <cfvo type="formula" val="$D$14"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E15">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$15/2"/>
-        <cfvo type="formula" val="$D$15"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$16/2"/>
-        <cfvo type="formula" val="$D$16"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17:E20">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D20">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$18/2"/>
-        <cfvo type="formula" val="$D$18"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D21">
     <cfRule type="colorScale" priority="20">
       <colorScale>
-        <cfvo type="formula" val="$D$21/2"/>
-        <cfvo type="formula" val="$D$21"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E22">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$22/2"/>
-        <cfvo type="formula" val="$D$22"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E23">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D23">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$23/2"/>
-        <cfvo type="formula" val="$D$23"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E24">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D24">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$24/2"/>
-        <cfvo type="formula" val="$D$24"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E25">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D25">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$25/2"/>
-        <cfvo type="formula" val="$D$25"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E26">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D26">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$26/2"/>
-        <cfvo type="formula" val="$D$26"/>
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>

--- a/data/Program Output KPIs by FTE.xlsx
+++ b/data/Program Output KPIs by FTE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B14545-5415-4732-98C1-BBA220A7E2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2626B721-5225-4DA6-8852-68B3362EF4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -101,9 +101,6 @@
     <t>KPI 7</t>
   </si>
   <si>
-    <t>Key Performance Indicator (KPI)</t>
-  </si>
-  <si>
     <t>Number of delivery partners trained</t>
   </si>
   <si>
@@ -198,6 +195,9 @@
   </si>
   <si>
     <t>Total Full Time Equivalent</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KPI</t>
   </si>
 </sst>
 </file>
@@ -631,6 +631,24 @@
     <xf numFmtId="1" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -641,24 +659,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1012,10 +1012,10 @@
     <row r="1" spans="1:9" s="1" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21"/>
       <c r="B1" s="22" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D1" s="52">
         <v>2025</v>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="22"/>
@@ -1052,7 +1052,7 @@
       <c r="I2" s="32"/>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="53" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="33" t="s">
@@ -1072,7 +1072,7 @@
       <c r="I3" s="37"/>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="58"/>
+      <c r="A4" s="54"/>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="10"/>
@@ -1089,7 +1089,7 @@
       <c r="I4" s="38"/>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="59"/>
+      <c r="A5" s="55"/>
       <c r="B5" s="39" t="s">
         <v>13</v>
       </c>
@@ -1107,14 +1107,14 @@
       <c r="I5" s="43"/>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="59" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="34">
         <f>113/133</f>
@@ -1127,10 +1127,10 @@
       <c r="I6" s="37"/>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A7" s="61"/>
-      <c r="B7" s="54"/>
+      <c r="A7" s="57"/>
+      <c r="B7" s="60"/>
       <c r="C7" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="20">
         <v>0.59</v>
@@ -1142,12 +1142,12 @@
       <c r="I7" s="38"/>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A8" s="61"/>
-      <c r="B8" s="55" t="s">
+      <c r="A8" s="57"/>
+      <c r="B8" s="61" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" s="17">
         <v>0.7</v>
@@ -1159,10 +1159,10 @@
       <c r="I8" s="38"/>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A9" s="61"/>
-      <c r="B9" s="55"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="61"/>
       <c r="C9" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="15">
         <v>0.49</v>
@@ -1174,12 +1174,12 @@
       <c r="I9" s="38"/>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="61"/>
-      <c r="B10" s="55" t="s">
+      <c r="A10" s="57"/>
+      <c r="B10" s="61" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" s="17">
         <v>89.4</v>
@@ -1191,10 +1191,10 @@
       <c r="I10" s="38"/>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A11" s="61"/>
-      <c r="B11" s="55"/>
+      <c r="A11" s="57"/>
+      <c r="B11" s="61"/>
       <c r="C11" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" s="15">
         <v>0.44</v>
@@ -1206,12 +1206,12 @@
       <c r="I11" s="38"/>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A12" s="61"/>
-      <c r="B12" s="55" t="s">
+      <c r="A12" s="57"/>
+      <c r="B12" s="61" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12" s="17">
         <f>1444/133</f>
@@ -1224,10 +1224,10 @@
       <c r="I12" s="38"/>
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="62"/>
-      <c r="B13" s="56"/>
+      <c r="A13" s="58"/>
+      <c r="B13" s="62"/>
       <c r="C13" s="45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="46">
         <v>0.34</v>
@@ -1239,14 +1239,14 @@
       <c r="I13" s="43"/>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="57" t="s">
+      <c r="A14" s="53" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" s="34">
         <v>0.3</v>
@@ -1258,12 +1258,12 @@
       <c r="I14" s="37"/>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A15" s="58"/>
+      <c r="A15" s="54"/>
       <c r="B15" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" s="16">
         <v>1.2E-2</v>
@@ -1275,12 +1275,12 @@
       <c r="I15" s="38"/>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A16" s="58"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
@@ -1292,9 +1292,9 @@
       <c r="I16" s="38"/>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A17" s="58"/>
+      <c r="A17" s="54"/>
       <c r="B17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>4</v>
@@ -1309,12 +1309,12 @@
       <c r="I17" s="38"/>
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="59"/>
+      <c r="A18" s="55"/>
       <c r="B18" s="39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D18" s="48">
         <v>0.1729</v>
@@ -1326,14 +1326,14 @@
       <c r="I18" s="43"/>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="53" t="s">
         <v>5</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" s="34">
         <v>1.052</v>
@@ -1345,9 +1345,9 @@
       <c r="I19" s="37"/>
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="58"/>
+      <c r="A20" s="54"/>
       <c r="B20" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>6</v>
@@ -1362,12 +1362,12 @@
       <c r="I20" s="38"/>
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A21" s="58"/>
+      <c r="A21" s="54"/>
       <c r="B21" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
         <v>6.0150375939849621E-2</v>
@@ -1379,12 +1379,12 @@
       <c r="I21" s="38"/>
     </row>
     <row r="22" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A22" s="58"/>
+      <c r="A22" s="54"/>
       <c r="B22" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D22" s="17">
         <v>0.13533834586466165</v>
@@ -1396,12 +1396,12 @@
       <c r="I22" s="38"/>
     </row>
     <row r="23" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="59"/>
+      <c r="A23" s="55"/>
       <c r="B23" s="39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D23" s="48">
         <v>0.22556390977443608</v>
@@ -1413,11 +1413,11 @@
       <c r="I23" s="43"/>
     </row>
     <row r="24" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="57" t="s">
+      <c r="A24" s="53" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" s="33" t="s">
         <v>8</v>
@@ -1432,9 +1432,9 @@
       <c r="I24" s="37"/>
     </row>
     <row r="25" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A25" s="58"/>
+      <c r="A25" s="54"/>
       <c r="B25" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
@@ -1449,9 +1449,9 @@
       <c r="I25" s="38"/>
     </row>
     <row r="26" spans="1:9" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="59"/>
+      <c r="A26" s="55"/>
       <c r="B26" s="39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C26" s="39" t="s">
         <v>10</v>
@@ -1467,6 +1467,7 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A24:A26"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A13"/>
     <mergeCell ref="A14:A18"/>
@@ -1475,7 +1476,6 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A24:A26"/>
   </mergeCells>
   <conditionalFormatting sqref="D3">
     <cfRule type="colorScale" priority="31">
